--- a/analise_financeiro/Pediatrico/apresentação-Pediatrico.xlsx
+++ b/analise_financeiro/Pediatrico/apresentação-Pediatrico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,25 +505,25 @@
         <v>5330</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10660</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -545,25 +545,25 @@
         <v>6713.01</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6713.01</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -589,17 +589,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -629,17 +629,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -669,17 +669,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -709,17 +709,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -749,17 +749,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -789,17 +789,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -829,17 +829,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -869,17 +869,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -949,17 +949,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -981,17 +981,17 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1004,10 +1004,10 @@
         <v>300</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15">
@@ -1021,17 +1021,17 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1061,17 +1061,17 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Japeri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1145,25 +1145,25 @@
         <v>6713.01</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6713.01</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1185,25 +1185,25 @@
         <v>7698.35</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7698.35</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1309,17 +1309,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1581,17 +1581,17 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         <v>300</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -1621,17 +1621,17 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1661,17 +1661,17 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Japeri</t>
+          <t>Paracambi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20/12 a 19/01</t>
+          <t>20/03 a 19/04</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1687,606 +1687,6 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ADENOIDECTOMIA PEDIÁTRICO</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>5330</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA- PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>6713.01</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>7698.35</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>23095.05</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>TRATAMENTO CIRÚRGICO DE PERFURAÇÃO DO SEPTO NASAL - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>6500</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CORREÇÃO CIRÚRGICO DE ESTRABISMO (ACIMA DE 2 MUSCULOS) - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>5255.28</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>HERNIOPLASTIA INGUINAL (BILATERAL) - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>5850</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>HERNIOPLASTIA UMBILICAL - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>5237.06</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ORQUIDOPEXIA BILATERAL - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>7157.78</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>TRATAMENTO CIRÚRGICO DE HIDROCELE - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3782.7</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CORRECAO DE HIPOSPADIA (1º TEMPO) - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>6608.86</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>PLASTICA TOTAL DO PENIS - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>6500</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>POSTECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>4850</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>CONSULTA PEDIATRICA OTORRINO</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>300</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>CONSULTA PEDIATRICA CIRURGIA GERAL</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>300</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Pediatrico</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Paracambi</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>20/12 a 19/01</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>CONSULTA PEDIATRICA OFTALMOLOGISTA</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>300</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
         <v>0</v>
       </c>
     </row>
